--- a/ANALYSIS/08-NATCOMMS-R2-FIGURES/Source_Data.xlsx
+++ b/ANALYSIS/08-NATCOMMS-R2-FIGURES/Source_Data.xlsx
@@ -21,8 +21,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDFig1c" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDFig2_sensitivity" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDFig3_regional" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable_SX_scores" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable_SY_counts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable_S1_scores" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable_S2_counts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig1c_weights" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig4a_UMAP" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,13 +34,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,7 +54,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,12 +62,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,37 +446,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>biobank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EAS</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publications</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>income_group</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
@@ -2793,17 +2807,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>uk_biobank_share_pct</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lmic_biobank_share_pct</t>
         </is>
@@ -2863,12 +2877,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>global_south_trial_share_pct</t>
         </is>
@@ -3097,22 +3111,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ntd</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ntd_pct</t>
         </is>
@@ -3353,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.0888888888888888</v>
       </c>
     </row>
     <row r="19">
@@ -3381,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07122507122507123</v>
+        <v>0.0712250712250712</v>
       </c>
     </row>
     <row r="21">
@@ -3423,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03834355828220859</v>
+        <v>0.0383435582822085</v>
       </c>
     </row>
     <row r="24">
@@ -3451,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02660281989890928</v>
+        <v>0.0266028198989092</v>
       </c>
     </row>
     <row r="26">
@@ -3497,97 +3511,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gap</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sii</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>has_ct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>stored</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>injury</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>matched</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>gsp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>pubs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dalys</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>gap_recalc</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>u_base</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_base</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>u_nopen_fixedw</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>u_nopen_repca</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>gap_nopen</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -3603,14 +3617,14 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002650634152814746</v>
+        <v>0.0026506341528147</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>91.65094727444799</v>
+        <v>91.650947274448</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -3630,22 +3644,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06196248267660358</v>
+        <v>0.0619624826766035</v>
       </c>
       <c r="M2" t="n">
         <v>95</v>
       </c>
       <c r="N2" t="n">
-        <v>91.65094727444799</v>
+        <v>91.650947274448</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>91.65094727444799</v>
+        <v>91.650947274448</v>
       </c>
       <c r="Q2" t="n">
-        <v>90.90206244804695</v>
+        <v>90.90206244804696</v>
       </c>
       <c r="R2" t="n">
         <v>95</v>
@@ -3664,7 +3678,7 @@
         <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00244345236569643</v>
+        <v>0.0024434523656964</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
@@ -3691,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002602330849425826</v>
+        <v>0.0026023308494258</v>
       </c>
       <c r="M3" t="n">
         <v>95</v>
@@ -3725,7 +3739,7 @@
         <v>95</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002412882400676608</v>
+        <v>0.0024128824006766</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
@@ -3752,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001579472943999023</v>
+        <v>0.0001579472943999</v>
       </c>
       <c r="M4" t="n">
         <v>95</v>
@@ -3786,7 +3800,7 @@
         <v>95</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002285813679918647</v>
+        <v>0.0022858136799186</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
@@ -3847,7 +3861,7 @@
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002201154129579663</v>
+        <v>0.0022011541295796</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
@@ -3908,7 +3922,7 @@
         <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002045034663751721</v>
+        <v>0.0020450346637517</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="b">
@@ -3969,7 +3983,7 @@
         <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002024959307163954</v>
+        <v>0.0020249593071639</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
@@ -4030,7 +4044,7 @@
         <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001973900245502591</v>
+        <v>0.0019739002455025</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
@@ -4091,7 +4105,7 @@
         <v>95</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001952733960933983</v>
+        <v>0.0019527339609339</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
@@ -4152,7 +4166,7 @@
         <v>95</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001866115373559296</v>
+        <v>0.0018661153735592</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
@@ -4213,10 +4227,10 @@
         <v>95</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001870889682322741</v>
+        <v>0.0018708896823227</v>
       </c>
       <c r="D12" t="n">
-        <v>9.383208999483607</v>
+        <v>9.383208999483609</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -4276,7 +4290,7 @@
         <v>95</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001421977300196886</v>
+        <v>0.0014219773001968</v>
       </c>
       <c r="D13" t="n">
         <v>7.075628467446561</v>
@@ -4339,7 +4353,7 @@
         <v>95</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002580130705609918</v>
+        <v>0.0025801307056099</v>
       </c>
       <c r="D14" t="n">
         <v>26.92028477206353</v>
@@ -4402,7 +4416,7 @@
         <v>95</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001640006899833679</v>
+        <v>0.0016400068998336</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
@@ -4429,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02142750851315263</v>
+        <v>0.0214275085131526</v>
       </c>
       <c r="M15" t="n">
         <v>95</v>
@@ -4463,7 +4477,7 @@
         <v>95</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001607423997484148</v>
+        <v>0.0016074239974841</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="b">
@@ -4524,7 +4538,7 @@
         <v>95</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001534270006231964</v>
+        <v>0.0015342700062319</v>
       </c>
       <c r="D17" t="n">
         <v>8.771301303703261</v>
@@ -4587,7 +4601,7 @@
         <v>95</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001582253607921302</v>
+        <v>0.0015822536079213</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
@@ -4648,7 +4662,7 @@
         <v>95</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001566270599141717</v>
+        <v>0.0015662705991417</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
@@ -4709,7 +4723,7 @@
         <v>95</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001500230398960412</v>
+        <v>0.0015002303989604</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
@@ -4757,7 +4771,7 @@
         <v>90</v>
       </c>
       <c r="S20" t="n">
-        <v>11.94968553459119</v>
+        <v>11.9496855345912</v>
       </c>
     </row>
     <row r="21">
@@ -4770,7 +4784,7 @@
         <v>95</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00139371573459357</v>
+        <v>0.0013937157345935</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
@@ -4831,7 +4845,7 @@
         <v>95</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002374436939135194</v>
+        <v>0.0023744369391351</v>
       </c>
       <c r="D22" t="n">
         <v>66.18166916124281</v>
@@ -4894,7 +4908,7 @@
         <v>80</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002263405825942755</v>
+        <v>0.0022634058259427</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
@@ -4955,7 +4969,7 @@
         <v>90</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001583241275511682</v>
+        <v>0.0015832412755116</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
@@ -5016,7 +5030,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001096978201530874</v>
+        <v>0.0010969782015308</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
@@ -5077,7 +5091,7 @@
         <v>90</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001408153213560581</v>
+        <v>0.0014081532135605</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
@@ -5138,7 +5152,7 @@
         <v>95</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002232556231319904</v>
+        <v>0.0022325562313199</v>
       </c>
       <c r="D27" t="n">
         <v>335.304244396997</v>
@@ -5167,7 +5181,7 @@
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2385892852142986</v>
+        <v>0.2385892852142985</v>
       </c>
       <c r="M27" t="n">
         <v>95</v>
@@ -5201,7 +5215,7 @@
         <v>95</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00215076794847846</v>
+        <v>0.0021507679484784</v>
       </c>
       <c r="D28" t="n">
         <v>160.482354010598</v>
@@ -5264,7 +5278,7 @@
         <v>95</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002146627986803651</v>
+        <v>0.0021466279868036</v>
       </c>
       <c r="D29" t="n">
         <v>258.5806508835351</v>
@@ -5327,7 +5341,7 @@
         <v>90</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001310825929977</v>
+        <v>0.0013108259299769</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
@@ -5366,7 +5380,7 @@
         <v>29</v>
       </c>
       <c r="P30" t="n">
-        <v>63.37130264417996</v>
+        <v>63.37130264417995</v>
       </c>
       <c r="Q30" t="n">
         <v>61.66870696724084</v>
@@ -5388,7 +5402,7 @@
         <v>95</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002016307786107063</v>
+        <v>0.002016307786107</v>
       </c>
       <c r="D31" t="n">
         <v>120.8707639643779</v>
@@ -5451,7 +5465,7 @@
         <v>95</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002033619908615947</v>
+        <v>0.0020336199086159</v>
       </c>
       <c r="D32" t="n">
         <v>292.2309491219915</v>
@@ -5514,7 +5528,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001873856759630144</v>
+        <v>0.0018738567596301</v>
       </c>
       <c r="D33" t="n">
         <v>131.4696623789321</v>
@@ -5577,7 +5591,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001722985529340804</v>
+        <v>0.0017229855293408</v>
       </c>
       <c r="D34" t="n">
         <v>53.82706708598314</v>
@@ -5640,7 +5654,7 @@
         <v>85</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001459500752389431</v>
+        <v>0.0014595007523894</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="b">
@@ -5701,7 +5715,7 @@
         <v>90</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001757705234922469</v>
+        <v>0.0017577052349224</v>
       </c>
       <c r="D36" t="n">
         <v>25.37424257317256</v>
@@ -5764,7 +5778,7 @@
         <v>85</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001389063545502722</v>
+        <v>0.0013890635455027</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="b">
@@ -5825,7 +5839,7 @@
         <v>95</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001778035773895681</v>
+        <v>0.0017780357738956</v>
       </c>
       <c r="D38" t="n">
         <v>187.8675218621689</v>
@@ -5888,7 +5902,7 @@
         <v>85</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001327906851656735</v>
+        <v>0.0013279068516567</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="b">
@@ -5949,7 +5963,7 @@
         <v>95</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001271437387913465</v>
+        <v>0.0012714373879134</v>
       </c>
       <c r="D40" t="n">
         <v>42.03694066719028</v>
@@ -6012,7 +6026,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>0.001177739468403161</v>
+        <v>0.0011777394684031</v>
       </c>
       <c r="D41" t="n">
         <v>23.4251093963109</v>
@@ -6075,7 +6089,7 @@
         <v>80</v>
       </c>
       <c r="C42" t="n">
-        <v>0.00138143717776984</v>
+        <v>0.0013814371777698</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="b">
@@ -6136,7 +6150,7 @@
         <v>95</v>
       </c>
       <c r="C43" t="n">
-        <v>0.001286263461224735</v>
+        <v>0.0012862634612247</v>
       </c>
       <c r="D43" t="n">
         <v>127.4284406574275</v>
@@ -6199,7 +6213,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001382734160870314</v>
+        <v>0.0013827341608703</v>
       </c>
       <c r="D44" t="n">
         <v>1070.371811958365</v>
@@ -6262,7 +6276,7 @@
         <v>50</v>
       </c>
       <c r="C45" t="n">
-        <v>0.002992485649883747</v>
+        <v>0.0029924856498837</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="b">
@@ -6323,7 +6337,7 @@
         <v>70</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00160387868527323</v>
+        <v>0.0016038786852732</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="b">
@@ -6384,7 +6398,7 @@
         <v>80</v>
       </c>
       <c r="C47" t="n">
-        <v>0.001310120220296085</v>
+        <v>0.001310120220296</v>
       </c>
       <c r="D47" t="n">
         <v>31.99406519721162</v>
@@ -6447,7 +6461,7 @@
         <v>82</v>
       </c>
       <c r="C48" t="n">
-        <v>0.001439178013242781</v>
+        <v>0.0014391780132427</v>
       </c>
       <c r="D48" t="n">
         <v>228.4770940717717</v>
@@ -6510,7 +6524,7 @@
         <v>70</v>
       </c>
       <c r="C49" t="n">
-        <v>0.001357700792141259</v>
+        <v>0.0013577007921412</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="b">
@@ -6571,7 +6585,7 @@
         <v>40</v>
       </c>
       <c r="C50" t="n">
-        <v>0.003346658311784267</v>
+        <v>0.0033466583117842</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="b">
@@ -6632,7 +6646,7 @@
         <v>70</v>
       </c>
       <c r="C51" t="n">
-        <v>0.001277360948733985</v>
+        <v>0.0012773609487339</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="b">
@@ -6693,7 +6707,7 @@
         <v>70</v>
       </c>
       <c r="C52" t="n">
-        <v>0.001171191921457648</v>
+        <v>0.0011711919214576</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="b">
@@ -6754,14 +6768,14 @@
         <v>60</v>
       </c>
       <c r="C53" t="n">
-        <v>0.001783686224371195</v>
+        <v>0.0017836862243711</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>52.76585711664276</v>
+        <v>52.76585711664275</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
@@ -6787,13 +6801,13 @@
         <v>60</v>
       </c>
       <c r="N53" t="n">
-        <v>52.76585711664276</v>
+        <v>52.76585711664275</v>
       </c>
       <c r="O53" t="n">
         <v>52</v>
       </c>
       <c r="P53" t="n">
-        <v>52.76585711664276</v>
+        <v>52.76585711664275</v>
       </c>
       <c r="Q53" t="n">
         <v>52.22250219791731</v>
@@ -6815,7 +6829,7 @@
         <v>50</v>
       </c>
       <c r="C54" t="n">
-        <v>0.002425660379230976</v>
+        <v>0.0024256603792309</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="b">
@@ -6876,7 +6890,7 @@
         <v>70</v>
       </c>
       <c r="C55" t="n">
-        <v>0.001591810025274754</v>
+        <v>0.0015918100252747</v>
       </c>
       <c r="D55" t="n">
         <v>50.00216501214532</v>
@@ -6939,7 +6953,7 @@
         <v>80</v>
       </c>
       <c r="C56" t="n">
-        <v>0.001052167965099216</v>
+        <v>0.0010521679650992</v>
       </c>
       <c r="D56" t="n">
         <v>109.0807674007097</v>
@@ -7002,7 +7016,7 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.001515035051852465</v>
+        <v>0.0015150350518524</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="b">
@@ -7063,7 +7077,7 @@
         <v>60</v>
       </c>
       <c r="C58" t="n">
-        <v>0.001481807208620012</v>
+        <v>0.00148180720862</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="b">
@@ -7124,7 +7138,7 @@
         <v>60</v>
       </c>
       <c r="C59" t="n">
-        <v>0.001434756559319794</v>
+        <v>0.0014347565593197</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="b">
@@ -7185,7 +7199,7 @@
         <v>50</v>
       </c>
       <c r="C60" t="n">
-        <v>0.002111943438649178</v>
+        <v>0.0021119434386491</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="b">
@@ -7246,7 +7260,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>0.001385719166137278</v>
+        <v>0.0013857191661372</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="b">
@@ -7307,7 +7321,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="n">
-        <v>0.001377759035676718</v>
+        <v>0.0013777590356767</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="b">
@@ -7368,7 +7382,7 @@
         <v>60</v>
       </c>
       <c r="C63" t="n">
-        <v>0.001316136680543423</v>
+        <v>0.0013161366805434</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="b">
@@ -7429,7 +7443,7 @@
         <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0009950762614607811</v>
+        <v>0.0009950762614607</v>
       </c>
       <c r="D64" t="n">
         <v>32.84397161114316</v>
@@ -7492,7 +7506,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="n">
-        <v>0.001228318782523274</v>
+        <v>0.0012283187825232</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="b">
@@ -7534,7 +7548,7 @@
         <v>46.10403080746966</v>
       </c>
       <c r="Q65" t="n">
-        <v>44.96313017870332</v>
+        <v>44.96313017870333</v>
       </c>
       <c r="R65" t="n">
         <v>60</v>
@@ -7553,7 +7567,7 @@
         <v>60</v>
       </c>
       <c r="C66" t="n">
-        <v>0.001225776039063931</v>
+        <v>0.0012257760390639</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="b">
@@ -7614,7 +7628,7 @@
         <v>60</v>
       </c>
       <c r="C67" t="n">
-        <v>0.001662605442106724</v>
+        <v>0.0016626054421067</v>
       </c>
       <c r="D67" t="n">
         <v>42.8282501015352</v>
@@ -7677,7 +7691,7 @@
         <v>60</v>
       </c>
       <c r="C68" t="n">
-        <v>0.001191213144920766</v>
+        <v>0.0011912131449207</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="b">
@@ -7738,7 +7752,7 @@
         <v>70</v>
       </c>
       <c r="C69" t="n">
-        <v>0.001220994046889246</v>
+        <v>0.0012209940468892</v>
       </c>
       <c r="D69" t="n">
         <v>228.8215678225599</v>
@@ -7767,7 +7781,7 @@
         <v>49</v>
       </c>
       <c r="L69" t="n">
-        <v>9.911653091017735</v>
+        <v>9.911653091017737</v>
       </c>
       <c r="M69" t="n">
         <v>70</v>
@@ -7801,7 +7815,7 @@
         <v>50</v>
       </c>
       <c r="C70" t="n">
-        <v>0.001854016212746501</v>
+        <v>0.0018540162127465</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="b">
@@ -7862,7 +7876,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="n">
-        <v>0.001160677056759596</v>
+        <v>0.0011606770567595</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="b">
@@ -7923,7 +7937,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="n">
-        <v>0.001043264288455248</v>
+        <v>0.0010432642884552</v>
       </c>
       <c r="D72" t="n">
         <v>194.0029191964809</v>
@@ -7986,7 +8000,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="n">
-        <v>0.001304627046920359</v>
+        <v>0.0013046270469203</v>
       </c>
       <c r="D73" t="n">
         <v>69.26574482790981</v>
@@ -8049,7 +8063,7 @@
         <v>50</v>
       </c>
       <c r="C74" t="n">
-        <v>0.001438655308447778</v>
+        <v>0.0014386553084477</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="b">
@@ -8110,7 +8124,7 @@
         <v>50</v>
       </c>
       <c r="C75" t="n">
-        <v>0.001418133382685483</v>
+        <v>0.0014181333826854</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="b">
@@ -8171,7 +8185,7 @@
         <v>50</v>
       </c>
       <c r="C76" t="n">
-        <v>0.001407469506375492</v>
+        <v>0.0014074695063754</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="b">
@@ -8232,7 +8246,7 @@
         <v>60</v>
       </c>
       <c r="C77" t="n">
-        <v>0.001391230849549174</v>
+        <v>0.0013912308495491</v>
       </c>
       <c r="D77" t="n">
         <v>1107.130254225344</v>
@@ -8295,7 +8309,7 @@
         <v>60</v>
       </c>
       <c r="C78" t="n">
-        <v>0.001086680917069316</v>
+        <v>0.0010866809170693</v>
       </c>
       <c r="D78" t="n">
         <v>51.21345341526204</v>
@@ -8358,7 +8372,7 @@
         <v>60</v>
       </c>
       <c r="C79" t="n">
-        <v>0.001261724857613444</v>
+        <v>0.0012617248576134</v>
       </c>
       <c r="D79" t="n">
         <v>158.9860889958423</v>
@@ -8421,7 +8435,7 @@
         <v>50</v>
       </c>
       <c r="C80" t="n">
-        <v>0.001328543410636485</v>
+        <v>0.0013285434106364</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="b">
@@ -8482,7 +8496,7 @@
         <v>50</v>
       </c>
       <c r="C81" t="n">
-        <v>0.001292684115469456</v>
+        <v>0.0012926841154694</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="b">
@@ -8543,7 +8557,7 @@
         <v>60</v>
       </c>
       <c r="C82" t="n">
-        <v>0.001188723486848176</v>
+        <v>0.0011887234868481</v>
       </c>
       <c r="D82" t="n">
         <v>227.5075714491467</v>
@@ -8594,7 +8608,7 @@
         <v>40</v>
       </c>
       <c r="C83" t="n">
-        <v>0.001876009744592011</v>
+        <v>0.001876009744592</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="b">
@@ -8655,7 +8669,7 @@
         <v>50</v>
       </c>
       <c r="C84" t="n">
-        <v>0.001755790668539703</v>
+        <v>0.0017557906685397</v>
       </c>
       <c r="D84" t="n">
         <v>180.0929610134687</v>
@@ -8718,7 +8732,7 @@
         <v>60</v>
       </c>
       <c r="C85" t="n">
-        <v>0.001097072963602841</v>
+        <v>0.0010970729636028</v>
       </c>
       <c r="D85" t="n">
         <v>439.8648701654163</v>
@@ -8781,7 +8795,7 @@
         <v>60</v>
       </c>
       <c r="C86" t="n">
-        <v>0.001031237188726664</v>
+        <v>0.0010312371887266</v>
       </c>
       <c r="D86" t="n">
         <v>404.6567737528345</v>
@@ -8844,7 +8858,7 @@
         <v>50</v>
       </c>
       <c r="C87" t="n">
-        <v>0.001098307315260172</v>
+        <v>0.0010983073152601</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="b">
@@ -8905,7 +8919,7 @@
         <v>50</v>
       </c>
       <c r="C88" t="n">
-        <v>0.001656451844610274</v>
+        <v>0.0016564518446102</v>
       </c>
       <c r="D88" t="n">
         <v>494.468585614081</v>
@@ -8968,7 +8982,7 @@
         <v>50</v>
       </c>
       <c r="C89" t="n">
-        <v>0.001519026700407267</v>
+        <v>0.0015190267004072</v>
       </c>
       <c r="D89" t="n">
         <v>140.7842916734805</v>
@@ -9031,7 +9045,7 @@
         <v>50</v>
       </c>
       <c r="C90" t="n">
-        <v>0.001505649648606777</v>
+        <v>0.0015056496486067</v>
       </c>
       <c r="D90" t="n">
         <v>270.9278400542476</v>
@@ -9094,7 +9108,7 @@
         <v>50</v>
       </c>
       <c r="C91" t="n">
-        <v>0.001403745962306857</v>
+        <v>0.0014037459623068</v>
       </c>
       <c r="D91" t="n">
         <v>189.5109305079395</v>
@@ -9157,7 +9171,7 @@
         <v>40</v>
       </c>
       <c r="C92" t="n">
-        <v>0.002060155384242535</v>
+        <v>0.0020601553842425</v>
       </c>
       <c r="D92" t="n">
         <v>197.6022134456051</v>
@@ -9220,7 +9234,7 @@
         <v>50</v>
       </c>
       <c r="C93" t="n">
-        <v>0.001324273296631873</v>
+        <v>0.0013242732966318</v>
       </c>
       <c r="D93" t="n">
         <v>134.9756077508528</v>
@@ -9283,7 +9297,7 @@
         <v>50</v>
       </c>
       <c r="C94" t="n">
-        <v>0.001375688938423991</v>
+        <v>0.0013756889384239</v>
       </c>
       <c r="D94" t="n">
         <v>857.2466930118169</v>
@@ -9346,7 +9360,7 @@
         <v>40</v>
       </c>
       <c r="C95" t="n">
-        <v>0.001493498682975769</v>
+        <v>0.0014934986829757</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="b">
@@ -9407,7 +9421,7 @@
         <v>40</v>
       </c>
       <c r="C96" t="n">
-        <v>0.001492153387516737</v>
+        <v>0.0014921533875167</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="b">
@@ -9434,7 +9448,7 @@
         <v>4</v>
       </c>
       <c r="L96" t="n">
-        <v>0.2854786136708956</v>
+        <v>0.2854786136708955</v>
       </c>
       <c r="M96" t="n">
         <v>40</v>
@@ -9468,7 +9482,7 @@
         <v>50</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0007773017860017717</v>
+        <v>0.0007773017860017</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="b">
@@ -9529,7 +9543,7 @@
         <v>40</v>
       </c>
       <c r="C98" t="n">
-        <v>0.001447016024030745</v>
+        <v>0.0014470160240307</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="b">
@@ -9590,7 +9604,7 @@
         <v>50</v>
       </c>
       <c r="C99" t="n">
-        <v>0.001067616976797581</v>
+        <v>0.0010676169767975</v>
       </c>
       <c r="D99" t="n">
         <v>77.4474339715107</v>
@@ -9653,7 +9667,7 @@
         <v>50</v>
       </c>
       <c r="C100" t="n">
-        <v>0.001177210826426744</v>
+        <v>0.0011772108264267</v>
       </c>
       <c r="D100" t="n">
         <v>567.735870258827</v>
@@ -9716,7 +9730,7 @@
         <v>50</v>
       </c>
       <c r="C101" t="n">
-        <v>0.001109151868149638</v>
+        <v>0.0011091518681496</v>
       </c>
       <c r="D101" t="n">
         <v>193.3602119398705</v>
@@ -9779,7 +9793,7 @@
         <v>30</v>
       </c>
       <c r="C102" t="n">
-        <v>0.001953362254425883</v>
+        <v>0.0019533622544258</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="b">
@@ -9840,7 +9854,7 @@
         <v>40</v>
       </c>
       <c r="C103" t="n">
-        <v>0.001262387610040605</v>
+        <v>0.0012623876100406</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="b">
@@ -9901,7 +9915,7 @@
         <v>40</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0016777110286057</v>
+        <v>0.0016777110286056</v>
       </c>
       <c r="D104" t="n">
         <v>223.7822840921361</v>
@@ -9964,7 +9978,7 @@
         <v>40</v>
       </c>
       <c r="C105" t="n">
-        <v>0.001481101498939097</v>
+        <v>0.001481101498939</v>
       </c>
       <c r="D105" t="n">
         <v>55.89811449730843</v>
@@ -10027,14 +10041,14 @@
         <v>40</v>
       </c>
       <c r="C106" t="n">
-        <v>0.00118977902457118</v>
+        <v>0.0011897790245711</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="b">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>29.36416315411055</v>
+        <v>29.36416315411054</v>
       </c>
       <c r="G106" t="b">
         <v>0</v>
@@ -10088,7 +10102,7 @@
         <v>40</v>
       </c>
       <c r="C107" t="n">
-        <v>0.001625814475119114</v>
+        <v>0.0016258144751191</v>
       </c>
       <c r="D107" t="n">
         <v>274.5567086538808</v>
@@ -10151,7 +10165,7 @@
         <v>50</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0008578640408813953</v>
+        <v>0.0008578640408813</v>
       </c>
       <c r="D108" t="n">
         <v>141.3222346844313</v>
@@ -10214,7 +10228,7 @@
         <v>40</v>
       </c>
       <c r="C109" t="n">
-        <v>0.001140387030318379</v>
+        <v>0.0011403870303183</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="b">
@@ -10275,7 +10289,7 @@
         <v>40</v>
       </c>
       <c r="C110" t="n">
-        <v>0.001578413299284875</v>
+        <v>0.0015784132992848</v>
       </c>
       <c r="D110" t="n">
         <v>828.0900911731338</v>
@@ -10304,7 +10318,7 @@
         <v>102</v>
       </c>
       <c r="L110" t="n">
-        <v>7.766063220113367</v>
+        <v>7.766063220113368</v>
       </c>
       <c r="M110" t="n">
         <v>40</v>
@@ -10338,7 +10352,7 @@
         <v>40</v>
       </c>
       <c r="C111" t="n">
-        <v>0.001437115715816617</v>
+        <v>0.0014371157158166</v>
       </c>
       <c r="D111" t="n">
         <v>259.4658160379183</v>
@@ -10401,10 +10415,10 @@
         <v>40</v>
       </c>
       <c r="C112" t="n">
-        <v>0.001440160325728357</v>
+        <v>0.0014401603257283</v>
       </c>
       <c r="D112" t="n">
-        <v>1445.140715750161</v>
+        <v>1445.140715750162</v>
       </c>
       <c r="E112" t="b">
         <v>1</v>
@@ -10464,7 +10478,7 @@
         <v>40</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00134656485170126</v>
+        <v>0.0013465648517012</v>
       </c>
       <c r="D113" t="n">
         <v>200.5135378077913</v>
@@ -10527,7 +10541,7 @@
         <v>40</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00131478370167315</v>
+        <v>0.0013147837016731</v>
       </c>
       <c r="D114" t="n">
         <v>228.3637929786822</v>
@@ -10571,7 +10585,7 @@
         <v>26.19957049702244</v>
       </c>
       <c r="Q114" t="n">
-        <v>25.90716090143866</v>
+        <v>25.90716090143865</v>
       </c>
       <c r="R114" t="n">
         <v>40</v>
@@ -10590,7 +10604,7 @@
         <v>40</v>
       </c>
       <c r="C115" t="n">
-        <v>0.001290683168917894</v>
+        <v>0.0012906831689178</v>
       </c>
       <c r="D115" t="n">
         <v>304.3842242310515</v>
@@ -10653,7 +10667,7 @@
         <v>40</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0008829605649225414</v>
+        <v>0.0008829605649225</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="b">
@@ -10714,7 +10728,7 @@
         <v>40</v>
       </c>
       <c r="C117" t="n">
-        <v>0.001278723473660648</v>
+        <v>0.0012787234736606</v>
       </c>
       <c r="D117" t="n">
         <v>331.4800758478517</v>
@@ -10777,7 +10791,7 @@
         <v>40</v>
       </c>
       <c r="C118" t="n">
-        <v>0.001193481031805277</v>
+        <v>0.0011934810318052</v>
       </c>
       <c r="D118" t="n">
         <v>229.2877806743368</v>
@@ -10812,13 +10826,13 @@
         <v>40</v>
       </c>
       <c r="N118" t="n">
-        <v>24.98918538829481</v>
+        <v>24.98918538829482</v>
       </c>
       <c r="O118" t="n">
         <v>117</v>
       </c>
       <c r="P118" t="n">
-        <v>24.98918538829481</v>
+        <v>24.98918538829482</v>
       </c>
       <c r="Q118" t="n">
         <v>24.5862458668056</v>
@@ -10840,7 +10854,7 @@
         <v>40</v>
       </c>
       <c r="C119" t="n">
-        <v>0.001208277302794158</v>
+        <v>0.0012082773027941</v>
       </c>
       <c r="D119" t="n">
         <v>342.7597916361639</v>
@@ -10903,7 +10917,7 @@
         <v>40</v>
       </c>
       <c r="C120" t="n">
-        <v>0.001190558657981455</v>
+        <v>0.0011905586579814</v>
       </c>
       <c r="D120" t="n">
         <v>522.6211453989846</v>
@@ -10966,7 +10980,7 @@
         <v>40</v>
       </c>
       <c r="C121" t="n">
-        <v>0.001154933590441942</v>
+        <v>0.0011549335904419</v>
       </c>
       <c r="D121" t="n">
         <v>268.5548152813323</v>
@@ -11029,7 +11043,7 @@
         <v>40</v>
       </c>
       <c r="C122" t="n">
-        <v>0.001110883895307779</v>
+        <v>0.0011108838953077</v>
       </c>
       <c r="D122" t="n">
         <v>283.2750899471721</v>
@@ -11092,7 +11106,7 @@
         <v>40</v>
       </c>
       <c r="C123" t="n">
-        <v>0.001107588992454112</v>
+        <v>0.0011075889924541</v>
       </c>
       <c r="D123" t="n">
         <v>265.5348062194414</v>
@@ -11155,7 +11169,7 @@
         <v>30</v>
       </c>
       <c r="C124" t="n">
-        <v>0.001692220568656921</v>
+        <v>0.0016922205686569</v>
       </c>
       <c r="D124" t="n">
         <v>499.5876420846482</v>
@@ -11190,13 +11204,13 @@
         <v>30</v>
       </c>
       <c r="N124" t="n">
-        <v>22.87715295991633</v>
+        <v>22.87715295991634</v>
       </c>
       <c r="O124" t="n">
         <v>123</v>
       </c>
       <c r="P124" t="n">
-        <v>22.87715295991633</v>
+        <v>22.87715295991634</v>
       </c>
       <c r="Q124" t="n">
         <v>23.19054753933128</v>
@@ -11218,7 +11232,7 @@
         <v>40</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0009677862981334329</v>
+        <v>0.0009677862981334</v>
       </c>
       <c r="D125" t="n">
         <v>607.3112146636123</v>
@@ -11281,7 +11295,7 @@
         <v>30</v>
       </c>
       <c r="C126" t="n">
-        <v>0.001594059518538415</v>
+        <v>0.0015940595185384</v>
       </c>
       <c r="D126" t="n">
         <v>584.061067866824</v>
@@ -11344,7 +11358,7 @@
         <v>30</v>
       </c>
       <c r="C127" t="n">
-        <v>0.001483294414356351</v>
+        <v>0.0014832944143563</v>
       </c>
       <c r="D127" t="n">
         <v>229.0499477862836</v>
@@ -11407,7 +11421,7 @@
         <v>30</v>
       </c>
       <c r="C128" t="n">
-        <v>0.001041031442582607</v>
+        <v>0.0010410314425826</v>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="b">
@@ -11468,7 +11482,7 @@
         <v>30</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0009785812580958009</v>
+        <v>0.0009785812580958</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="b">
@@ -11495,7 +11509,7 @@
         <v>1049</v>
       </c>
       <c r="L129" t="n">
-        <v>27.73763589398563</v>
+        <v>27.73763589398562</v>
       </c>
       <c r="M129" t="n">
         <v>30</v>
@@ -11529,7 +11543,7 @@
         <v>30</v>
       </c>
       <c r="C130" t="n">
-        <v>0.001276454306207597</v>
+        <v>0.0012764543062075</v>
       </c>
       <c r="D130" t="n">
         <v>657.4653574711598</v>
@@ -11573,7 +11587,7 @@
         <v>18.67101090787472</v>
       </c>
       <c r="Q130" t="n">
-        <v>18.60603240440339</v>
+        <v>18.60603240440338</v>
       </c>
       <c r="R130" t="n">
         <v>30</v>
@@ -11592,7 +11606,7 @@
         <v>30</v>
       </c>
       <c r="C131" t="n">
-        <v>0.001264370046555996</v>
+        <v>0.0012643700465559</v>
       </c>
       <c r="D131" t="n">
         <v>637.6417079134754</v>
@@ -11655,7 +11669,7 @@
         <v>30</v>
       </c>
       <c r="C132" t="n">
-        <v>0.001240332145243883</v>
+        <v>0.0012403321452438</v>
       </c>
       <c r="D132" t="n">
         <v>646.0927629186546</v>
@@ -11664,7 +11678,7 @@
         <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>18.31495603672979</v>
+        <v>18.31495603672978</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
@@ -11718,7 +11732,7 @@
         <v>20</v>
       </c>
       <c r="C133" t="n">
-        <v>0.001619178103283048</v>
+        <v>0.001619178103283</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="b">
@@ -11779,7 +11793,7 @@
         <v>20</v>
       </c>
       <c r="C134" t="n">
-        <v>0.001766316243447363</v>
+        <v>0.0017663162434473</v>
       </c>
       <c r="D134" t="n">
         <v>118.1910289950771</v>
@@ -11842,7 +11856,7 @@
         <v>30</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0008730750996619463</v>
+        <v>0.0008730750996619</v>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="b">
@@ -11903,7 +11917,7 @@
         <v>30</v>
       </c>
       <c r="C136" t="n">
-        <v>0.001052956562489271</v>
+        <v>0.0010529565624892</v>
       </c>
       <c r="D136" t="n">
         <v>295.8882451884695</v>
@@ -11966,7 +11980,7 @@
         <v>20</v>
       </c>
       <c r="C137" t="n">
-        <v>0.001469019101932645</v>
+        <v>0.0014690191019326</v>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="b">
@@ -12027,7 +12041,7 @@
         <v>20</v>
       </c>
       <c r="C138" t="n">
-        <v>0.001282505341805518</v>
+        <v>0.0012825053418055</v>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="b">
@@ -12088,7 +12102,7 @@
         <v>10</v>
       </c>
       <c r="C139" t="n">
-        <v>0.00216803140938282</v>
+        <v>0.0021680314093828</v>
       </c>
       <c r="D139" t="n">
         <v>1695.537770086243</v>
@@ -12111,13 +12125,13 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>13.90863916152625</v>
+        <v>13.90863916152626</v>
       </c>
       <c r="O139" t="n">
         <v>138</v>
       </c>
       <c r="P139" t="n">
-        <v>13.90863916152625</v>
+        <v>13.90863916152626</v>
       </c>
       <c r="Q139" t="n">
         <v>15.17560167004641</v>
@@ -12139,7 +12153,7 @@
         <v>20</v>
       </c>
       <c r="C140" t="n">
-        <v>0.001458851154893637</v>
+        <v>0.0014588511548936</v>
       </c>
       <c r="D140" t="n">
         <v>1256.047215778535</v>
@@ -12183,7 +12197,7 @@
         <v>13.63135922268123</v>
       </c>
       <c r="Q140" t="n">
-        <v>13.99259814742561</v>
+        <v>13.9925981474256</v>
       </c>
       <c r="R140" t="n">
         <v>20</v>
@@ -12202,7 +12216,7 @@
         <v>20</v>
       </c>
       <c r="C141" t="n">
-        <v>0.001163916545920074</v>
+        <v>0.00116391654592</v>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="b">
@@ -12263,7 +12277,7 @@
         <v>20</v>
       </c>
       <c r="C142" t="n">
-        <v>0.001322188414633274</v>
+        <v>0.0013221884146332</v>
       </c>
       <c r="D142" t="n">
         <v>5178.221244966196</v>
@@ -12326,7 +12340,7 @@
         <v>20</v>
       </c>
       <c r="C143" t="n">
-        <v>0.001069325837306678</v>
+        <v>0.0010693258373066</v>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="b">
@@ -12387,7 +12401,7 @@
         <v>20</v>
       </c>
       <c r="C144" t="n">
-        <v>0.001173170167021453</v>
+        <v>0.0011731701670214</v>
       </c>
       <c r="D144" t="n">
         <v>837.0630570110864</v>
@@ -12450,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="C145" t="n">
-        <v>0.001068481826223433</v>
+        <v>0.0010684818262234</v>
       </c>
       <c r="D145" t="n">
         <v>415.2039631124421</v>
@@ -12494,13 +12508,13 @@
         <v>9.964571502459435</v>
       </c>
       <c r="Q145" t="n">
-        <v>9.968245526075053</v>
+        <v>9.968245526075052</v>
       </c>
       <c r="R145" t="n">
         <v>20</v>
       </c>
       <c r="S145" t="n">
-        <v>90.56603773584905</v>
+        <v>90.56603773584904</v>
       </c>
     </row>
     <row r="146">
@@ -12513,7 +12527,7 @@
         <v>20</v>
       </c>
       <c r="C146" t="n">
-        <v>0.001036127214320004</v>
+        <v>0.00103612721432</v>
       </c>
       <c r="D146" t="n">
         <v>385.5154042490142</v>
@@ -12576,7 +12590,7 @@
         <v>20</v>
       </c>
       <c r="C147" t="n">
-        <v>0.001050455030053854</v>
+        <v>0.0010504550300538</v>
       </c>
       <c r="D147" t="n">
         <v>730.1902395680941</v>
@@ -12626,7 +12640,7 @@
         <v>20</v>
       </c>
       <c r="S147" t="n">
-        <v>91.82389937106919</v>
+        <v>91.8238993710692</v>
       </c>
     </row>
     <row r="148">
@@ -12639,7 +12653,7 @@
         <v>20</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0007941341609694064</v>
+        <v>0.0007941341609694</v>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="b">
@@ -12700,7 +12714,7 @@
         <v>10</v>
       </c>
       <c r="C149" t="n">
-        <v>0.001290822634473443</v>
+        <v>0.0012908226344734</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="b">
@@ -12727,7 +12741,7 @@
         <v>1445</v>
       </c>
       <c r="L149" t="n">
-        <v>1.215448670136497</v>
+        <v>1.215448670136498</v>
       </c>
       <c r="M149" t="n">
         <v>10</v>
@@ -12748,7 +12762,7 @@
         <v>10</v>
       </c>
       <c r="S149" t="n">
-        <v>93.08176100628931</v>
+        <v>93.08176100628933</v>
       </c>
     </row>
     <row r="150">
@@ -12761,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C150" t="n">
-        <v>0.001241681631654501</v>
+        <v>0.0012416816316545</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="b">
@@ -12809,7 +12823,7 @@
         <v>10</v>
       </c>
       <c r="S150" t="n">
-        <v>93.71069182389937</v>
+        <v>93.71069182389935</v>
       </c>
     </row>
     <row r="151">
@@ -12822,7 +12836,7 @@
         <v>10</v>
       </c>
       <c r="C151" t="n">
-        <v>0.001218379125930369</v>
+        <v>0.0012183791259303</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="b">
@@ -12883,7 +12897,7 @@
         <v>10</v>
       </c>
       <c r="C152" t="n">
-        <v>0.001197487115859985</v>
+        <v>0.0011974871158599</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="b">
@@ -12910,7 +12924,7 @@
         <v>227</v>
       </c>
       <c r="L152" t="n">
-        <v>1.747546241583507</v>
+        <v>1.747546241583508</v>
       </c>
       <c r="M152" t="n">
         <v>10</v>
@@ -12931,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="S152" t="n">
-        <v>94.96855345911949</v>
+        <v>94.96855345911948</v>
       </c>
     </row>
     <row r="153">
@@ -12944,7 +12958,7 @@
         <v>10</v>
       </c>
       <c r="C153" t="n">
-        <v>0.001232433365657926</v>
+        <v>0.0012324333656579</v>
       </c>
       <c r="D153" t="n">
         <v>3507.660623100643</v>
@@ -13007,7 +13021,7 @@
         <v>10</v>
       </c>
       <c r="C154" t="n">
-        <v>0.001151194563135505</v>
+        <v>0.0011511945631355</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
@@ -13055,7 +13069,7 @@
         <v>10</v>
       </c>
       <c r="S154" t="n">
-        <v>96.22641509433963</v>
+        <v>96.22641509433964</v>
       </c>
     </row>
     <row r="155">
@@ -13068,7 +13082,7 @@
         <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>0.001194234471768141</v>
+        <v>0.0011942344717681</v>
       </c>
       <c r="D155" t="n">
         <v>716.9893922698778</v>
@@ -13131,7 +13145,7 @@
         <v>10</v>
       </c>
       <c r="C156" t="n">
-        <v>0.001111685647629201</v>
+        <v>0.0011116856476292</v>
       </c>
       <c r="D156" t="n">
         <v>1138.099176141538</v>
@@ -13181,7 +13195,7 @@
         <v>10</v>
       </c>
       <c r="S156" t="n">
-        <v>97.48427672955975</v>
+        <v>97.48427672955977</v>
       </c>
     </row>
     <row r="157">
@@ -13194,7 +13208,7 @@
         <v>10</v>
       </c>
       <c r="C157" t="n">
-        <v>0.00111151160672307</v>
+        <v>0.001111511606723</v>
       </c>
       <c r="D157" t="n">
         <v>2466.931379321135</v>
@@ -13244,7 +13258,7 @@
         <v>10</v>
       </c>
       <c r="S157" t="n">
-        <v>98.11320754716981</v>
+        <v>98.11320754716979</v>
       </c>
     </row>
     <row r="158">
@@ -13257,7 +13271,7 @@
         <v>10</v>
       </c>
       <c r="C158" t="n">
-        <v>0.001019828370772302</v>
+        <v>0.0010198283707723</v>
       </c>
       <c r="D158" t="n">
         <v>4305.669095392587</v>
@@ -13320,7 +13334,7 @@
         <v>10</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0009351730113849044</v>
+        <v>0.0009351730113849</v>
       </c>
       <c r="D159" t="n">
         <v>6307.031066979047</v>
@@ -13370,7 +13384,7 @@
         <v>10</v>
       </c>
       <c r="S159" t="n">
-        <v>99.37106918238993</v>
+        <v>99.37106918238992</v>
       </c>
     </row>
     <row r="160">
@@ -13383,7 +13397,7 @@
         <v>10</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0008187407511286438</v>
+        <v>0.0008187407511285999</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="b">
@@ -13449,22 +13463,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>biobanks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>publications</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mean_EAS</t>
         </is>
@@ -13581,67 +13595,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>category_published</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gap_score_published</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>unified_score_published</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rank_published</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>category_corrected</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gap_score_corrected</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unified_score_corrected</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rank_corrected</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dalys</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>low_measured_burden</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>category_changed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rank_change</t>
         </is>
@@ -21130,37 +21144,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>biobank_publications_published</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>biobank_publications_corrected</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>trials_published</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>trials_corrected</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>trial_intensity_published</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>trial_intensity_corrected</t>
         </is>
@@ -24904,6 +24918,3456 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pc1_explained_variance</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_complete_cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E176"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>umap_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>umap_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_papers</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sii</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Acne_vulgaris</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8.237789154052734</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.523589491844177</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16412</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0013857191661372</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Acute_glomerulonephritis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9.770922660827637</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3055483400821686</v>
+      </c>
+      <c r="D3" t="n">
+        <v>32647</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.001619178103283</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Acute_hepatitis</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8.490594863891602</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.398892641067505</v>
+      </c>
+      <c r="D4" t="n">
+        <v>105425</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0013912308495491</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adverse_effects_of_medical_treatment</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9.281656265258787</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.116169452667236</v>
+      </c>
+      <c r="D5" t="n">
+        <v>115362</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0009187364485114</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>African_trypanosomiasis</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.523406505584717</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.311449527740479</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4845</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0026506341528147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Age-related_and_other_hearing_loss</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11.08063411712646</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.545873165130615</v>
+      </c>
+      <c r="D7" t="n">
+        <v>80002</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0014347565593197</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alcohol_use_disorders</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12.14520359039307</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.726121425628662</v>
+      </c>
+      <c r="D8" t="n">
+        <v>39037</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0017663162434473</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alopecia_areata</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8.290266990661621</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.485413312911987</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4415</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0014690191019326</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alzheimer's_disease_and_other_dementias</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11.79482078552246</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.016077518463135</v>
+      </c>
+      <c r="D10" t="n">
+        <v>204293</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0014832944143563</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Animal_contact</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8.648828506469727</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.703323125839233</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10211</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0017884545959532</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Anxiety_disorders</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12.10743045806885</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.786760330200195</v>
+      </c>
+      <c r="D12" t="n">
+        <v>61312</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0020601553842425</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aortic_aneurysm</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9.970719337463381</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.38283121585846</v>
+      </c>
+      <c r="D13" t="n">
+        <v>48286</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0019533622544258</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Appendicitis</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8.933929443359375</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8591563701629639</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16121</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0017836862243711</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Asthma</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9.741729736328123</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7580034136772156</v>
+      </c>
+      <c r="D15" t="n">
+        <v>142197</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0011934810318052</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Atrial_fibrillation_and_flutter</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10.61112880706787</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.30525267124176</v>
+      </c>
+      <c r="D16" t="n">
+        <v>101534</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0016922205686569</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Attention-deficit_hyperactivity_disorder</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12.26566505432129</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.890438079833984</v>
+      </c>
+      <c r="D17" t="n">
+        <v>44908</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0021680314093828</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Autism_spectrum_disorders</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12.19797039031982</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.289376735687256</v>
+      </c>
+      <c r="D18" t="n">
+        <v>94640</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0017557906685397</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bacterial_skin_diseases</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7.585931777954102</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.72780704498291</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14283</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0013890635455027</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bipolar_disorder</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12.35669040679932</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.631776332855225</v>
+      </c>
+      <c r="D20" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0016777110286056</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bladder_cancer</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8.198003768920898</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.188974022865295</v>
+      </c>
+      <c r="D21" t="n">
+        <v>54009</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0011905586579814</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Blindness_and_vision_loss</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11.09469509124756</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.337538480758667</v>
+      </c>
+      <c r="D22" t="n">
+        <v>55325</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0013147837016731</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brain_and_central_nervous_system_cancer</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8.256536483764648</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.456190586090088</v>
+      </c>
+      <c r="D23" t="n">
+        <v>155117</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0011772108264267</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Breast_cancer</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8.574604034423828</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.191894292831421</v>
+      </c>
+      <c r="D24" t="n">
+        <v>219224</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0010504550300538</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8.777247428894043</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.665720462799072</v>
+      </c>
+      <c r="D25" t="n">
+        <v>52153</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0016626054421067</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cardiomyopathy_and_myocarditis</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10.39750385284424</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.06846010684967</v>
+      </c>
+      <c r="D26" t="n">
+        <v>109826</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0013242732966318</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cervical_cancer</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8.681399345397949</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.8319736123085022</v>
+      </c>
+      <c r="D27" t="n">
+        <v>77362</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0012209940468892</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chagas_disease</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6.607539653778076</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.170293807983398</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17438</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0022325562313199</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chronic_kidney_disease</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>10.35010147094727</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5092151165008545</v>
+      </c>
+      <c r="D29" t="n">
+        <v>136989</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0012906831689178</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chronic_obstructive_pulmonary_disease</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>10.0355281829834</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8246358633041382</v>
+      </c>
+      <c r="D30" t="n">
+        <v>73460</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0013046270469203</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cirrhosis_and_other_chronic_liver_diseases</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9.053120613098145</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1521524637937545</v>
+      </c>
+      <c r="D31" t="n">
+        <v>115444</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0011108838953077</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colon_and_rectum_cancer</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8.328405380249023</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.7575590014457703</v>
+      </c>
+      <c r="D32" t="n">
+        <v>190757</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.00103612721432</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Conduct_disorder</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12.01322746276856</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.848031044006348</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6012</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0033466583117842</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Conflict_and_terrorism</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9.934963226318359</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.93806529045105</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15089</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0024434633087366</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Congenital_birth_defects</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10.8521842956543</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.886544108390808</v>
+      </c>
+      <c r="D35" t="n">
+        <v>207110</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.0012617248576134</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cystic_echinococcosis</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6.720605373382568</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.42028546333313</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11794</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0022011541295796</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6.543154239654541</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.531447172164917</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4651</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0020249593071639</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Decubitus_ulcer</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>10.27616024017334</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.580791234970093</v>
+      </c>
+      <c r="D38" t="n">
+        <v>13194</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0013577007921412</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7.051988124847412</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.471061229705811</v>
+      </c>
+      <c r="D39" t="n">
+        <v>29945</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0018738567596301</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Depressive_disorders</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>12.15019512176514</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.596221923828125</v>
+      </c>
+      <c r="D40" t="n">
+        <v>227813</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0013465648517012</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dermatitis</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>8.290684700012207</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.63024640083313</v>
+      </c>
+      <c r="D41" t="n">
+        <v>77689</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0011549335904419</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Diabetes_mellitus</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>10.57190799713135</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6063776016235352</v>
+      </c>
+      <c r="D42" t="n">
+        <v>231620</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0010529565624892</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Diarrheal_diseases</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>8.384443283081055</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.89438533782959</v>
+      </c>
+      <c r="D43" t="n">
+        <v>115871</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0010521679650992</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dietary_iron_deficiency</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>11.09858131408691</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6849833726882935</v>
+      </c>
+      <c r="D44" t="n">
+        <v>22514</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0011777394684031</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>8.223679542541504</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.985244274139404</v>
+      </c>
+      <c r="D45" t="n">
+        <v>9165</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0016074239974841</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Drowning</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>9.82156467437744</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3.353965997695923</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4323</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0017017978243529</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Drug_use_disorders</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>11.88726234436035</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.606973171234131</v>
+      </c>
+      <c r="D47" t="n">
+        <v>177601</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0016564518446102</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Eating_disorders</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>12.32593059539795</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4.813316345214844</v>
+      </c>
+      <c r="D48" t="n">
+        <v>51541</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0014371157158166</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7.218038082122803</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.597176551818848</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10194</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0024434523656964</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Encephalitis</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8.121853828430176</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.852108001708984</v>
+      </c>
+      <c r="D50" t="n">
+        <v>47767</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0013937157345935</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Endocarditis</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>9.811673164367676</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.568228960037231</v>
+      </c>
+      <c r="D51" t="n">
+        <v>25786</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0018540162127465</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Endocrine,_metabolic,_blood,_and_immune_disorders</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>10.44327449798584</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5931628942489624</v>
+      </c>
+      <c r="D52" t="n">
+        <v>219891</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0008187407511285999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Environmental_heat_and_cold_exposure</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>9.807032585144045</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.611835479736328</v>
+      </c>
+      <c r="D53" t="n">
+        <v>10160</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0014730727998539</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Esophageal_cancer</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7.731133937835693</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.7839607000350952</v>
+      </c>
+      <c r="D54" t="n">
+        <v>51432</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0014074695063754</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Exposure_to_forces_of_nature</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>9.467823028564451</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.792699098587036</v>
+      </c>
+      <c r="D55" t="n">
+        <v>27992</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0024256603792309</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Exposure_to_mechanical_forces</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10.41082286834717</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.289393186569214</v>
+      </c>
+      <c r="D56" t="n">
+        <v>17810</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.0014608186902478</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Eye_cancer</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7.731709480285645</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2.087031364440918</v>
+      </c>
+      <c r="D57" t="n">
+        <v>20518</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.00148180720862</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Falls</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10.47652816772461</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2.98470401763916</v>
+      </c>
+      <c r="D58" t="n">
+        <v>17388</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.0017663032049313</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Fire,_heat,_and_hot_substances</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>9.930244445800779</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2.572971105575562</v>
+      </c>
+      <c r="D59" t="n">
+        <v>30292</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0012508762301877</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Food-borne_trematodiases</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>6.432930469512939</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3.653030395507813</v>
+      </c>
+      <c r="D60" t="n">
+        <v>17465</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.0019527339609339</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Foreign_body</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>9.4700927734375</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2.03441333770752</v>
+      </c>
+      <c r="D61" t="n">
+        <v>32632</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.0020018785726279</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Fungal_skin_diseases</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7.406026840209961</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.75423002243042</v>
+      </c>
+      <c r="D62" t="n">
+        <v>12452</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.0022634058259427</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gallbladder_and_biliary_diseases</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>8.770556449890137</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0240585133433341</v>
+      </c>
+      <c r="D63" t="n">
+        <v>62746</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0011897790245711</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gallbladder_and_biliary_tract_cancer</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>7.920955181121826</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.620072603225708</v>
+      </c>
+      <c r="D64" t="n">
+        <v>17652</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.0014386553084477</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gout</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>10.08973693847656</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.3341040015220642</v>
+      </c>
+      <c r="D65" t="n">
+        <v>12818</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.0011974871158599</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guinea_worm_disease</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6.637666702270508</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4.097343921661377</v>
+      </c>
+      <c r="D66" t="n">
+        <v>429</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0022858136799186</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gynecological_diseases</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>8.84201717376709</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.698585033416748</v>
+      </c>
+      <c r="D67" t="n">
+        <v>207352</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0009785812580958</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HIV_AIDS</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>8.471019744873047</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.472359180450439</v>
+      </c>
+      <c r="D68" t="n">
+        <v>222246</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0011887234868481</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Headache_disorders</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10.79543018341064</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.352283716201782</v>
+      </c>
+      <c r="D69" t="n">
+        <v>99995</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.0010866809170693</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hemoglobinopathies_and_hemolytic_anemias</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>10.96738052368164</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1.062169075012207</v>
+      </c>
+      <c r="D70" t="n">
+        <v>38043</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.0012862634612247</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Hodgkin_lymphoma</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>8.529006958007812</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-2.018703460693359</v>
+      </c>
+      <c r="D71" t="n">
+        <v>27318</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.0014181333826854</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hypertensive_heart_disease</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10.63448333740234</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.871038556098938</v>
+      </c>
+      <c r="D72" t="n">
+        <v>228464</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0010684818262234</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Idiopathic_developmental_intellectual_disability</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>11.50945568084717</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3.290771484375</v>
+      </c>
+      <c r="D73" t="n">
+        <v>63611</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.0014934986829757</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Idiopathic_epilepsy</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>11.32693958282471</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2.521214485168457</v>
+      </c>
+      <c r="D74" t="n">
+        <v>74509</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.0014037459623068</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Inflammatory_bowel_disease</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>8.691743850708008</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.3322556316852569</v>
+      </c>
+      <c r="D75" t="n">
+        <v>95884</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.001111511606723</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Inguinal,_femoral,_and_abdominal_hernia</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>9.064845085144045</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.060554146766663</v>
+      </c>
+      <c r="D76" t="n">
+        <v>13350</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.0021119434386491</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Interpersonal_violence</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>11.56216335296631</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4.753633499145508</v>
+      </c>
+      <c r="D77" t="n">
+        <v>86268</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.0023984920699149</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Interstitial_lung_disease_and_pulmonary_sarcoidosis</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>9.594034194946287</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.6988533139228821</v>
+      </c>
+      <c r="D78" t="n">
+        <v>59081</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.0010970729636028</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Intestinal_nematode_infections</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>6.353782176971436</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3.740359544754028</v>
+      </c>
+      <c r="D79" t="n">
+        <v>26256</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.002016307786107</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Invasive_Non-typhoidal_Salmonella_(iNTS)</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7.691750049591064</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3.636794805526733</v>
+      </c>
+      <c r="D80" t="n">
+        <v>13791</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.0020450346637517</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Iodine_deficiency</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>11.29945182800293</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.6187143921852112</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3368</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.0019739002455025</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ischemic_heart_disease</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10.54027652740478</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1.198721528053284</v>
+      </c>
+      <c r="D82" t="n">
+        <v>109356</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.001481101498939</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Kidney_cancer</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>8.052266120910645</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-1.679634094238281</v>
+      </c>
+      <c r="D83" t="n">
+        <v>67556</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.0012643700465559</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Larynx_cancer</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>7.521325588226318</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.25225305557251</v>
+      </c>
+      <c r="D84" t="n">
+        <v>14243</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.0013777590356767</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Leishmaniasis</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>6.490751266479492</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.128643035888672</v>
+      </c>
+      <c r="D85" t="n">
+        <v>24632</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.0021466279868036</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7.247087478637695</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3.310894966125488</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8452</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.0016400068998336</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Leukemia</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>8.59473991394043</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.775201797485352</v>
+      </c>
+      <c r="D87" t="n">
+        <v>192887</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.0013756889384239</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Lip_and_oral_cavity_cancer</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7.571329593658447</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.439555287361145</v>
+      </c>
+      <c r="D88" t="n">
+        <v>57156</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.0011711919214576</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Liver_cancer</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8.095956802368164</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.7127144932746887</v>
+      </c>
+      <c r="D89" t="n">
+        <v>156561</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.0012787234736606</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Low_back_pain</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>10.51603984832764</v>
+      </c>
+      <c r="C90" t="n">
+        <v>2.525593519210815</v>
+      </c>
+      <c r="D90" t="n">
+        <v>40563</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.0015918100252747</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Lower_extremity_peripheral_arterial_disease</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10.36643886566162</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1.778441667556763</v>
+      </c>
+      <c r="D91" t="n">
+        <v>52741</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.0010410314425826</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Lower_respiratory_infections</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>8.555741310119629</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3.13182520866394</v>
+      </c>
+      <c r="D92" t="n">
+        <v>174866</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.0010432642884552</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Lymphatic_filariasis</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>6.412025451660156</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3.97377347946167</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3354</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.0023744369391351</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>6.824577808380127</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4.07958459854126</v>
+      </c>
+      <c r="D94" t="n">
+        <v>78894</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.0017577052349224</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Malignant_neoplasm_of_bone_and_articular_cartilage</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>7.660501003265381</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.987654685974121</v>
+      </c>
+      <c r="D95" t="n">
+        <v>72852</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.0012257760390639</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Malignant_skin_melanoma</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>8.409153938293457</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.729212164878845</v>
+      </c>
+      <c r="D96" t="n">
+        <v>120427</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.00116391654592</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Maternal_disorders</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>11.18580532073975</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1.024428963661194</v>
+      </c>
+      <c r="D97" t="n">
+        <v>197490</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.0012403321452438</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>8.061594009399414</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4.091579914093018</v>
+      </c>
+      <c r="D98" t="n">
+        <v>15392</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.0015832412755116</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8.160276412963867</v>
+      </c>
+      <c r="C99" t="n">
+        <v>2.883755683898926</v>
+      </c>
+      <c r="D99" t="n">
+        <v>42140</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.0012714373879134</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Mesothelioma</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>8.100048065185547</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.880497336387634</v>
+      </c>
+      <c r="D100" t="n">
+        <v>14334</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.0012283187825232</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Motor_neuron_disease</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>11.78805160522461</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3.050122499465942</v>
+      </c>
+      <c r="D101" t="n">
+        <v>52517</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0014588511548936</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Multiple_myeloma</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>8.732819557189941</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.809366106987</v>
+      </c>
+      <c r="D102" t="n">
+        <v>45115</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.0014401603257283</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Multiple_sclerosis</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>11.56122493743896</v>
+      </c>
+      <c r="C103" t="n">
+        <v>2.676352977752686</v>
+      </c>
+      <c r="D103" t="n">
+        <v>90164</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.0012324333656579</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Nasopharynx_cancer</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>7.939611434936523</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.107800722122192</v>
+      </c>
+      <c r="D104" t="n">
+        <v>24915</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.0011912131449207</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Neck_pain</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>10.62073040008545</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2.445649862289429</v>
+      </c>
+      <c r="D105" t="n">
+        <v>16475</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.0016038786852732</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Neonatal_disorders</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>11.0849142074585</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1.706590414047241</v>
+      </c>
+      <c r="D106" t="n">
+        <v>222965</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0009950762614607</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Neuroblastoma_and_other_peripheral_nervous_cell_tumors</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>8.48890495300293</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.596929669380188</v>
+      </c>
+      <c r="D107" t="n">
+        <v>34075</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.0014921533875167</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Non-Hodgkin_lymphoma</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>8.468938827514648</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-2.127590656280518</v>
+      </c>
+      <c r="D108" t="n">
+        <v>70213</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.0015784132992848</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Non-melanoma_skin_cancer</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>7.606509685516357</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.250110149383545</v>
+      </c>
+      <c r="D109" t="n">
+        <v>102183</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.0012416816316545</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Non-rheumatic_valvular_heart_disease</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>10.32511615753174</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1.360207438468933</v>
+      </c>
+      <c r="D110" t="n">
+        <v>77007</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.001876009744592</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Onchocerciasis</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>6.498384475708008</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.077162742614746</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2345</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.0025801307056099</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oral_disorders</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>9.974997520446776</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1.986165881156922</v>
+      </c>
+      <c r="D112" t="n">
+        <v>192917</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.0010983073152601</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Osteoarthritis</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>10.54958152770996</v>
+      </c>
+      <c r="C113" t="n">
+        <v>2.183493852615356</v>
+      </c>
+      <c r="D113" t="n">
+        <v>114321</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.0015056496486067</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Other_cardiovascular_and_circulatory_diseases</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>10.4232234954834</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1.172872543334961</v>
+      </c>
+      <c r="D114" t="n">
+        <v>210283</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.0009351730113849</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Other_chronic_respiratory_diseases</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>9.869338035583496</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.7972744703292847</v>
+      </c>
+      <c r="D115" t="n">
+        <v>99873</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.0010693258373066</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Other_digestive_diseases</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>8.793249130249023</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.1008185893297195</v>
+      </c>
+      <c r="D116" t="n">
+        <v>218025</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.0007941341609694</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Other_intestinal_infectious_diseases</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>8.250588417053223</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2.365617990493774</v>
+      </c>
+      <c r="D117" t="n">
+        <v>25413</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.0010969782015308</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Other_malignant_neoplasms</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>7.939349174499512</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.729079127311706</v>
+      </c>
+      <c r="D118" t="n">
+        <v>221347</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.0010198283707723</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Other_mental_disorders</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12.28889465332031</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.376341819763184</v>
+      </c>
+      <c r="D119" t="n">
+        <v>219665</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.0013221884146332</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Other_musculoskeletal_disorders</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>10.45772361755371</v>
+      </c>
+      <c r="C120" t="n">
+        <v>2.052002906799316</v>
+      </c>
+      <c r="D120" t="n">
+        <v>219603</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.0009677862981334</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Other_neglected_tropical_diseases</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>6.826314449310303</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4.376856327056885</v>
+      </c>
+      <c r="D121" t="n">
+        <v>12657</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.0015342700062319</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Other_neoplasms</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>7.607341766357422</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.837431788444519</v>
+      </c>
+      <c r="D122" t="n">
+        <v>112046</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.0012908226344734</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Other_neurological_disorders</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>11.15077209472656</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2.249664068222046</v>
+      </c>
+      <c r="D123" t="n">
+        <v>220012</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.0008730750996619</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Other_nutritional_deficiencies</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>11.22644519805908</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.535879909992218</v>
+      </c>
+      <c r="D124" t="n">
+        <v>72403</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.0012183791259303</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Other_pharynx_cancer</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>7.602610111236572</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.094963788986206</v>
+      </c>
+      <c r="D125" t="n">
+        <v>27592</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.0012926841154694</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Other_sense_organ_diseases</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>11.05663585662842</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2.449759244918823</v>
+      </c>
+      <c r="D126" t="n">
+        <v>99493</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0012773609487339</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Other_skin_and_subcutaneous_diseases</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>8.376270294189453</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5787639617919922</v>
+      </c>
+      <c r="D127" t="n">
+        <v>204666</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.0007773017860017</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Other_transport_injuries</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>9.918588638305664</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3.68841814994812</v>
+      </c>
+      <c r="D128" t="n">
+        <v>759</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.0028017770964652</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Other_unintentional_injuries</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>9.782362937927246</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.080241680145264</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4626</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.0016581196105107</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Other_unspecified_infectious_diseases</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>8.318916320800781</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.662580251693726</v>
+      </c>
+      <c r="D130" t="n">
+        <v>211595</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.0011403870303183</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Otitis_media</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>8.922892570495605</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2.839445114135742</v>
+      </c>
+      <c r="D131" t="n">
+        <v>17536</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.0014081532135605</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ovarian_cancer</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>8.466608047485352</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.27429187297821</v>
+      </c>
+      <c r="D132" t="n">
+        <v>88730</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.0011942344717681</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Pancreatic_cancer</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>8.148491859436035</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.9655774831771852</v>
+      </c>
+      <c r="D133" t="n">
+        <v>87717</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.0012082773027941</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Pancreatitis</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>8.983137130737305</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.1915368735790252</v>
+      </c>
+      <c r="D134" t="n">
+        <v>48066</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.0011091518681496</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Paralytic_ileus_and_intestinal_obstruction</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>8.967264175415039</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.9736053347587584</v>
+      </c>
+      <c r="D135" t="n">
+        <v>23965</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.0019359302241355</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Parkinson's_disease</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>11.8823652267456</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.157183885574341</v>
+      </c>
+      <c r="D136" t="n">
+        <v>140133</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.0015940595185384</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>8.332781791687012</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.92414402961731</v>
+      </c>
+      <c r="D137" t="n">
+        <v>15935</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.0015822536079213</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Pneumoconiosis</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>9.472410202026367</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.171264171600342</v>
+      </c>
+      <c r="D138" t="n">
+        <v>5837</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.0013285434106364</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Poisonings</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>9.104270935058594</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2.522383689880371</v>
+      </c>
+      <c r="D139" t="n">
+        <v>91498</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0011631571687757</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Police_conflict_and_executions</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>11.2564640045166</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4.55067777633667</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2599</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.0029924856498837</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Prostate_cancer</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>8.51651668548584</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.125884413719177</v>
+      </c>
+      <c r="D141" t="n">
+        <v>164684</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.0011731701670214</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Protein-energy_malnutrition</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>11.08968830108643</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.4929287731647491</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2931</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.0014391780132427</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Pruritus</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>8.479389190673828</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.631976246833801</v>
+      </c>
+      <c r="D143" t="n">
+        <v>19806</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.0011606770567595</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Psoriasis</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>8.439023971557617</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1.252241611480713</v>
+      </c>
+      <c r="D144" t="n">
+        <v>47484</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.0012764543062075</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Pulmonary_Arterial_Hypertension</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>10.19784736633301</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.8727656602859497</v>
+      </c>
+      <c r="D145" t="n">
+        <v>52658</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.0012623876100406</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>7.344769477844238</v>
+      </c>
+      <c r="C146" t="n">
+        <v>4.496366500854492</v>
+      </c>
+      <c r="D146" t="n">
+        <v>9674</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.0017780357738956</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Rheumatic_heart_disease</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>10.29382801055908</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1.406246304512024</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.0014219773001968</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Rheumatoid_arthritis</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>9.419775009155272</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.5012719631195068</v>
+      </c>
+      <c r="D148" t="n">
+        <v>111424</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.0011116856476292</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Road_injuries</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>9.90534782409668</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3.416385889053345</v>
+      </c>
+      <c r="D149" t="n">
+        <v>30365</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0019125139806419</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Scabies</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>6.996404647827148</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.100806951522827</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2871</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.0018661153735592</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Schistosomiasis</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>6.471807956695557</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3.814296245574951</v>
+      </c>
+      <c r="D151" t="n">
+        <v>14232</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0017229855293408</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Schizophrenia</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>12.43580055236816</v>
+      </c>
+      <c r="C152" t="n">
+        <v>4.452438354492188</v>
+      </c>
+      <c r="D152" t="n">
+        <v>123827</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.0016258144751191</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Self-harm</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>11.82070064544678</v>
+      </c>
+      <c r="C153" t="n">
+        <v>4.616251945495605</v>
+      </c>
+      <c r="D153" t="n">
+        <v>58732</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.0019858838059008</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Sexually_transmitted_infections_excluding_HIV</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>8.369293212890625</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3.613310098648071</v>
+      </c>
+      <c r="D154" t="n">
+        <v>203014</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.0013827341608703</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Soft_tissue_and_other_extraosseous_sarcomas</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>7.737012386322021</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-2.086791753768921</v>
+      </c>
+      <c r="D155" t="n">
+        <v>69865</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.0013161366805434</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Stomach_cancer</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>7.986116409301758</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.7866616249084473</v>
+      </c>
+      <c r="D156" t="n">
+        <v>103320</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.0015190267004072</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Stroke</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>10.61836528778076</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1.544046401977539</v>
+      </c>
+      <c r="D157" t="n">
+        <v>213448</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.0010676169767975</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Sudden_infant_death_syndrome</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>10.17962455749512</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3.201379537582397</v>
+      </c>
+      <c r="D158" t="n">
+        <v>4695</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.0014595007523894</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Testicular_cancer</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>7.812118530273437</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.978962302207947</v>
+      </c>
+      <c r="D159" t="n">
+        <v>12763</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.0014470160240307</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>8.260603904724121</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4.040665626525879</v>
+      </c>
+      <c r="D160" t="n">
+        <v>12379</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.0015002303989604</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Thyroid_cancer</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>7.649265766143799</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.526372194290161</v>
+      </c>
+      <c r="D161" t="n">
+        <v>52209</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0012825053418055</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Tracheal,_bronchus,_and_lung_cancer</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>8.054733276367188</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.9872297048568726</v>
+      </c>
+      <c r="D162" t="n">
+        <v>188000</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.0011075889924541</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Trachoma</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>7.467033863067627</v>
+      </c>
+      <c r="C163" t="n">
+        <v>4.059771537780762</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2072</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0020336199086159</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>7.567426681518555</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.364124298095703</v>
+      </c>
+      <c r="D164" t="n">
+        <v>142560</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.001310120220296</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Typhoid_and_paratyphoid</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>7.558489322662354</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3.784565925598145</v>
+      </c>
+      <c r="D165" t="n">
+        <v>6240</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0018708896823227</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Upper_digestive_system_diseases</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>8.538957595825195</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.1390172094106674</v>
+      </c>
+      <c r="D166" t="n">
+        <v>216009</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0008578640408813</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Upper_respiratory_infections</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>8.493972778320312</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.215823888778687</v>
+      </c>
+      <c r="D167" t="n">
+        <v>176702</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.0010312371887266</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Urinary_diseases_and_male_infertility</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>9.871686935424805</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.2100670039653778</v>
+      </c>
+      <c r="D168" t="n">
+        <v>217013</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.0008829605649225</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Urticaria</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>8.42349910736084</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1.702760696411133</v>
+      </c>
+      <c r="D169" t="n">
+        <v>15762</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.0013814371777698</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Uterine_cancer</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>8.72984790802002</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.8859681487083435</v>
+      </c>
+      <c r="D170" t="n">
+        <v>96168</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.0011511945631355</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Varicella_and_herpes_zoster</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>8.210874557495117</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2.964503526687622</v>
+      </c>
+      <c r="D171" t="n">
+        <v>15389</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.0013108259299769</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Vascular_intestinal_disorders</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>9.255038261413574</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.2239782363176345</v>
+      </c>
+      <c r="D172" t="n">
+        <v>4226</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.0015150350518524</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Viral_skin_diseases</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>7.968254089355469</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2.585062026977539</v>
+      </c>
+      <c r="D173" t="n">
+        <v>9983</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.0013279068516567</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Vitamin_A_deficiency</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>11.2771167755127</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.6641881465911865</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3135</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.0015662705991417</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Yellow_fever</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>7.147083759307861</v>
+      </c>
+      <c r="C175" t="n">
+        <v>4.576414108276367</v>
+      </c>
+      <c r="D175" t="n">
+        <v>5685</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.0021507679484784</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Zika_virus</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>7.158198833465576</v>
+      </c>
+      <c r="C176" t="n">
+        <v>4.714966773986816</v>
+      </c>
+      <c r="D176" t="n">
+        <v>12776</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.0024128824006766</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24920,12 +28384,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>mean_EAS</t>
         </is>
@@ -25236,12 +28700,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>income_group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>publications</t>
         </is>
@@ -25282,17 +28746,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sites</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>income</t>
         </is>
@@ -25538,42 +29002,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>gsDiseaseCount</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gsTrials</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gsTrialsPct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gsDALYs</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gsDALYsPct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gsIntensity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nonGsIntensity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>intensityGap</t>
         </is>
@@ -25620,37 +29084,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_papers</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>SII</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>KTP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>RCC</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>global_south_priority</t>
         </is>
@@ -30396,47 +33860,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>unified_score</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gap_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ct_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sii</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dimensions_available</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dalys</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>low_measured_burden</t>
         </is>
@@ -31345,47 +34809,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>unified_score</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gap_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ct_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sii</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dimensions_available</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dalys</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>low_measured_burden</t>
         </is>
@@ -31696,47 +35160,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>unified_score</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gap_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ct_equity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sii</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dimensions_available</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dalys</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>low_measured_burden</t>
         </is>
